--- a/data/performance/daily/signal_list_2026-07-28.xlsx
+++ b/data/performance/daily/signal_list_2026-07-28.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-07-28.xlsx
+++ b/data/performance/daily/signal_list_2026-07-28.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -642,17 +658,22 @@
       <c r="G7" s="4" t="n">
         <v>3.05</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>1.29</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -728,15 +754,20 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -770,15 +801,20 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -812,15 +848,20 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>6.77</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -896,15 +942,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -936,17 +987,22 @@
       <c r="G14" s="4" t="n">
         <v>4.56</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -980,15 +1036,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1022,15 +1083,20 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1062,17 +1128,22 @@
       <c r="G17" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1106,15 +1177,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1148,15 +1224,20 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1188,17 +1269,22 @@
       <c r="G20" s="4" t="n">
         <v>2.91</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1230,17 +1316,22 @@
       <c r="G21" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1272,17 +1363,22 @@
       <c r="G22" s="4" t="n">
         <v>21.43</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1316,15 +1412,20 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,17 +1457,22 @@
       <c r="G24" s="4" t="n">
         <v>-4.38</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1400,15 +1506,20 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1440,17 +1551,22 @@
       <c r="G26" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1482,17 +1598,22 @@
       <c r="G27" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1524,17 +1645,22 @@
       <c r="G28" s="4" t="n">
         <v>1.76</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1566,17 +1692,22 @@
       <c r="G29" s="4" t="n">
         <v>-2.86</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1608,17 +1739,22 @@
       <c r="G30" s="4" t="n">
         <v>2.54</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1650,17 +1786,22 @@
       <c r="G31" s="4" t="n">
         <v>3.36</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1692,17 +1833,22 @@
       <c r="G32" s="4" t="n">
         <v>-4.62</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1736,15 +1882,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1778,15 +1929,20 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1818,17 +1974,22 @@
       <c r="G35" s="4" t="n">
         <v>2.08</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1860,17 +2021,22 @@
       <c r="G36" s="4" t="n">
         <v>3.11</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1904,15 +2070,20 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1944,17 +2115,22 @@
       <c r="G38" s="4" t="n">
         <v>-2.38</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1971,7 +2147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1981,9 +2157,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2013,7 +2190,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2038,15 +2215,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2078,17 +2260,22 @@
       <c r="G5" s="4" t="n">
         <v>24.73</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2120,17 +2307,22 @@
       <c r="G6" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2162,17 +2354,22 @@
       <c r="G7" s="4" t="n">
         <v>24.73</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2204,17 +2401,22 @@
       <c r="G8" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2246,17 +2448,22 @@
       <c r="G9" s="4" t="n">
         <v>-3.28</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G10" s="4" t="n">
         <v>1.55</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2330,17 +2542,22 @@
       <c r="G11" s="4" t="n">
         <v>-1.64</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2372,17 +2589,22 @@
       <c r="G12" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2416,15 +2638,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2458,15 +2685,20 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2500,15 +2732,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2540,17 +2777,22 @@
       <c r="G16" s="4" t="n">
         <v>7.23</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2584,15 +2826,20 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2626,15 +2873,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2668,15 +2920,20 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2710,15 +2967,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2752,15 +3014,20 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2794,15 +3061,20 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2836,15 +3108,20 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2876,17 +3153,22 @@
       <c r="G24" s="4" t="n">
         <v>-7.1</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2920,15 +3202,20 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2962,15 +3249,20 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3004,15 +3296,20 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,17 +3341,22 @@
       <c r="G28" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3086,17 +3388,22 @@
       <c r="G29" s="4" t="n">
         <v>2.91</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3128,17 +3435,22 @@
       <c r="G30" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3170,17 +3482,22 @@
       <c r="G31" s="4" t="n">
         <v>-8.369999999999999</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3214,15 +3531,20 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3254,17 +3576,22 @@
       <c r="G33" s="4" t="n">
         <v>-9.74</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3298,15 +3625,20 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3340,15 +3672,20 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3382,15 +3719,20 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3422,17 +3764,22 @@
       <c r="G37" s="4" t="n">
         <v>4.92</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3466,15 +3813,20 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3508,15 +3860,20 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3550,15 +3907,20 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3590,17 +3952,22 @@
       <c r="G41" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3632,17 +3999,22 @@
       <c r="G42" s="4" t="n">
         <v>9.59</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3674,17 +4046,22 @@
       <c r="G43" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3718,15 +4095,20 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3760,15 +4142,20 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,17 +4187,22 @@
       <c r="G46" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3842,17 +4234,22 @@
       <c r="G47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3884,17 +4281,22 @@
       <c r="G48" s="4" t="n">
         <v>2.54</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3928,15 +4330,20 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3970,15 +4377,20 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4012,15 +4424,20 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4052,17 +4469,22 @@
       <c r="G52" s="4" t="n">
         <v>-4.62</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4096,15 +4518,20 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4136,17 +4563,22 @@
       <c r="G54" s="4" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4178,17 +4610,22 @@
       <c r="G55" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4220,17 +4657,22 @@
       <c r="G56" s="4" t="n">
         <v>-3.75</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4264,15 +4706,20 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4306,15 +4753,20 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4348,15 +4800,20 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4390,15 +4847,20 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4430,17 +4892,22 @@
       <c r="G61" s="4" t="n">
         <v>-3.06</v>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4474,15 +4941,20 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4516,15 +4988,20 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4558,15 +5035,20 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4600,15 +5082,20 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4642,15 +5129,20 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-07-28.xlsx
+++ b/data/performance/daily/signal_list_2026-07-28.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>38850</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>38425</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>40000</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>2.96</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-1.09</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>1455</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>1445</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1455</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>2620</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>2700</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2720</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>3.82</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>3.05</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>775</v>
       </c>
       <c r="D8" t="n">
-        <v>785</v>
+        <v/>
       </c>
       <c r="E8" t="n">
         <v>785</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>1.29</v>
+      <c r="F8" t="n">
+        <v>785</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1.29</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H8" s="4" t="n">
+        <v>1.29</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>515</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>515</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>520</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>4240</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>4240</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>4250</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>332</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>332</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>338</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>1.81</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>1255</v>
       </c>
       <c r="D12" t="n">
-        <v>1340</v>
+        <v/>
       </c>
       <c r="E12" t="n">
         <v>1340</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>6.77</v>
+      <c r="F12" t="n">
+        <v>1340</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>6.77</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H12" s="4" t="n">
+        <v>6.77</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>97</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>119</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>15.53</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-5.83</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>17550</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>18350</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>18750</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>6.84</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>4.56</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>1205</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>1200</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1230</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>2.07</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-0.41</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>50</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>52</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.96</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-1.96</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>1720</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>1735</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>1755</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>2.03</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>1760</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>1730</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1775</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>725</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>725</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>730</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>515</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>530</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>570</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>10.68</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>2.91</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>200</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>192</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>200</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>630</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>765</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>785</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>24.6</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>21.43</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>63</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>59</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>70</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>11.11</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-6.35</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>137</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>131</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>137</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-4.38</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>254</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>228</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>256</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-10.24</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>244</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>234</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>244</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>190</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>192</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>206</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>8.42</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1634,33 +1709,36 @@
         <v>8500</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>8650</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>8925</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>1.76</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>525</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>510</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>520</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>-0.95</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-2.86</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>472</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>484</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>494</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>4.66</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>2.54</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>745</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>770</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>780</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>3.36</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>65</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>62</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>65</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-4.62</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1869,33 +1959,36 @@
         <v>296</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>290</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>302</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>2.03</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-2.03</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>222</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>220</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>226</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>720</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>735</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>750</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>2.08</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2010,33 +2109,36 @@
         <v>193</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>199</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>206</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>6.74</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>3.11</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2057,33 +2159,36 @@
         <v>212</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>206</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>214</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-2.83</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2104,33 +2209,36 @@
         <v>2520</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>2460</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>2520</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-2.38</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2147,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2155,12 +2263,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2190,45 +2299,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>1375</v>
       </c>
       <c r="D5" t="n">
-        <v>1715</v>
+        <v/>
       </c>
       <c r="E5" t="n">
         <v>1715</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>24.73</v>
+      <c r="F5" t="n">
+        <v>1715</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>24.73</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H5" s="4" t="n">
+        <v>24.73</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>1455</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>1445</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1455</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>1375</v>
       </c>
       <c r="D7" t="n">
-        <v>1715</v>
+        <v/>
       </c>
       <c r="E7" t="n">
         <v>1715</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>24.73</v>
+      <c r="F7" t="n">
+        <v>1715</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>24.73</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H7" s="4" t="n">
+        <v>24.73</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>224</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>276</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>24.32</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>610</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>590</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>595</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>-2.46</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-3.28</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>258</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>262</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>264</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>2.33</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>1.55</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>366</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>360</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>362</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>-1.09</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-1.64</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>442</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>444</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>456</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>3.17</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>159</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>152</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>165</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>3.77</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>103</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>97</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>119</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>15.53</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-5.83</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>1205</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>1200</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1230</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>2.07</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-0.41</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>166</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>178</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>220</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>32.53</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>7.23</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>2630</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>2610</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>2730</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>3.8</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>51</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>50</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>52</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.96</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-1.96</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>79</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>76</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>80</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-3.8</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>131</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>131</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>137</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3001,33 +3163,36 @@
         <v>124</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>121</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>128</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>3.23</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-2.42</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>4710</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>4680</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>4820</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>2.34</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>424</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>424</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>432</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>775</v>
       </c>
       <c r="D24" t="n">
-        <v>720</v>
+        <v/>
       </c>
       <c r="E24" t="n">
         <v>720</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>-7.1</v>
+      <c r="F24" t="n">
+        <v>720</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>-7.1</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H24" s="4" t="n">
+        <v>-7.1</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>114</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>107</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>115</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-6.14</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>64</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>63</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>66</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3283,33 +3463,36 @@
         <v>248</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>232</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>250</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>-6.45</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,33 +3513,36 @@
         <v>266</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>324</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>332</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>24.81</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,33 +3563,36 @@
         <v>515</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>530</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>570</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>10.68</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>2.91</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>200</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>192</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>200</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>1195</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>1095</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>1195</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>-8.369999999999999</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>166</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>160</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>197</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>18.67</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-3.61</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>975</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>880</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>970</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-9.74</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>133</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>125</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>144</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>8.27</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-6.02</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>114</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>113</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>116</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-0.88</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3706,33 +3913,36 @@
         <v>63</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>59</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>70</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>11.11</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-6.35</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3753,33 +3963,36 @@
         <v>122</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>130</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>6.56</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>4.92</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,33 +4013,36 @@
         <v>210</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>194</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>234</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>11.43</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-7.62</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,33 +4063,36 @@
         <v>216</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>189</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>270</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3894,33 +4113,36 @@
         <v>254</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>228</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>256</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>-10.24</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3941,33 +4163,36 @@
         <v>244</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>234</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>244</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3988,33 +4213,36 @@
         <v>73</v>
       </c>
       <c r="D42" t="n">
-        <v>80</v>
+        <v/>
       </c>
       <c r="E42" t="n">
         <v>80</v>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>9.59</v>
+      <c r="F42" t="n">
+        <v>80</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>9.59</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H42" s="4" t="n">
+        <v>9.59</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4035,33 +4263,36 @@
         <v>154</v>
       </c>
       <c r="D43" t="n">
+        <v/>
+      </c>
+      <c r="E43" t="n">
         <v>156</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>157</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>1.95</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4082,33 +4313,36 @@
         <v>121</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>117</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>124</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>2.48</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>-3.31</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4129,33 +4363,36 @@
         <v>226</v>
       </c>
       <c r="D45" t="n">
+        <v/>
+      </c>
+      <c r="E45" t="n">
         <v>224</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>230</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>1.77</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-0.88</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4176,33 +4413,36 @@
         <v>1085</v>
       </c>
       <c r="D46" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
         <v>1090</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>1095</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4223,33 +4463,36 @@
         <v>100</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>101</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>105</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4270,33 +4513,36 @@
         <v>472</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>484</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>494</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>4.66</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>2.54</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4317,33 +4563,36 @@
         <v>70</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>67</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>72</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>-4.29</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4364,33 +4613,36 @@
         <v>68</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>67</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>70</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>-1.47</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4411,33 +4663,36 @@
         <v>278</v>
       </c>
       <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
         <v>270</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>286</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>2.88</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>-2.88</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4458,33 +4713,36 @@
         <v>65</v>
       </c>
       <c r="D52" t="n">
+        <v/>
+      </c>
+      <c r="E52" t="n">
         <v>62</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>65</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>-4.62</v>
       </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4505,33 +4763,36 @@
         <v>111</v>
       </c>
       <c r="D53" t="n">
+        <v/>
+      </c>
+      <c r="E53" t="n">
         <v>111</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>115</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>3.6</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4552,33 +4813,36 @@
         <v>835</v>
       </c>
       <c r="D54" t="n">
+        <v/>
+      </c>
+      <c r="E54" t="n">
         <v>905</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>920</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>10.18</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4599,33 +4863,36 @@
         <v>74</v>
       </c>
       <c r="D55" t="n">
+        <v/>
+      </c>
+      <c r="E55" t="n">
         <v>75</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>78</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>5.41</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4646,33 +4913,36 @@
         <v>800</v>
       </c>
       <c r="D56" t="n">
+        <v/>
+      </c>
+      <c r="E56" t="n">
         <v>770</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>795</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>-3.75</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4693,33 +4963,36 @@
         <v>296</v>
       </c>
       <c r="D57" t="n">
+        <v/>
+      </c>
+      <c r="E57" t="n">
         <v>290</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>302</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>2.03</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>-2.03</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4740,33 +5013,36 @@
         <v>64</v>
       </c>
       <c r="D58" t="n">
+        <v/>
+      </c>
+      <c r="E58" t="n">
         <v>63</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>66</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4787,33 +5063,36 @@
         <v>72</v>
       </c>
       <c r="D59" t="n">
+        <v/>
+      </c>
+      <c r="E59" t="n">
         <v>71</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>73</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4834,33 +5113,36 @@
         <v>61</v>
       </c>
       <c r="D60" t="n">
+        <v/>
+      </c>
+      <c r="E60" t="n">
         <v>60</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>63</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>3.28</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>-1.64</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4881,33 +5163,36 @@
         <v>98</v>
       </c>
       <c r="D61" t="n">
+        <v/>
+      </c>
+      <c r="E61" t="n">
         <v>95</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>98</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>-3.06</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4928,33 +5213,36 @@
         <v>93</v>
       </c>
       <c r="D62" t="n">
+        <v/>
+      </c>
+      <c r="E62" t="n">
         <v>88</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>98</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>5.38</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>-5.38</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4975,33 +5263,36 @@
         <v>133</v>
       </c>
       <c r="D63" t="n">
+        <v/>
+      </c>
+      <c r="E63" t="n">
         <v>127</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>135</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="G63" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>-4.51</v>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5022,33 +5313,36 @@
         <v>212</v>
       </c>
       <c r="D64" t="n">
+        <v/>
+      </c>
+      <c r="E64" t="n">
         <v>206</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>214</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="H64" s="4" t="n">
         <v>-2.83</v>
       </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5069,33 +5363,36 @@
         <v>159</v>
       </c>
       <c r="D65" t="n">
+        <v/>
+      </c>
+      <c r="E65" t="n">
         <v>159</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>162</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5116,33 +5413,36 @@
         <v>238</v>
       </c>
       <c r="D66" t="n">
+        <v/>
+      </c>
+      <c r="E66" t="n">
         <v>236</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>250</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="G66" s="4" t="n">
         <v>5.04</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <v>-0.84</v>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-07-28.xlsx
+++ b/data/performance/daily/signal_list_2026-07-28.xlsx
@@ -559,7 +559,7 @@
         <v>38850</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>39150</v>
       </c>
       <c r="E5" t="n">
         <v>38425</v>
@@ -609,7 +609,7 @@
         <v>1455</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>1405.34</v>
       </c>
       <c r="E6" t="n">
         <v>1445</v>
@@ -659,7 +659,7 @@
         <v>2620</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>2640</v>
       </c>
       <c r="E7" t="n">
         <v>2700</v>
@@ -709,7 +709,7 @@
         <v>775</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>775</v>
       </c>
       <c r="E8" t="n">
         <v>785</v>
@@ -759,7 +759,7 @@
         <v>515</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>515</v>
       </c>
       <c r="E9" t="n">
         <v>515</v>
@@ -809,7 +809,7 @@
         <v>4240</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>4240</v>
       </c>
       <c r="E10" t="n">
         <v>4240</v>
@@ -859,7 +859,7 @@
         <v>332</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>334</v>
       </c>
       <c r="E11" t="n">
         <v>332</v>
@@ -909,7 +909,7 @@
         <v>1255</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>1260</v>
       </c>
       <c r="E12" t="n">
         <v>1340</v>
@@ -959,7 +959,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>103</v>
       </c>
       <c r="E13" t="n">
         <v>97</v>
@@ -1009,7 +1009,7 @@
         <v>17550</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>17550</v>
       </c>
       <c r="E14" t="n">
         <v>18350</v>
@@ -1059,7 +1059,7 @@
         <v>1205</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1210</v>
       </c>
       <c r="E15" t="n">
         <v>1200</v>
@@ -1109,7 +1109,7 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
         <v>50</v>
@@ -1159,7 +1159,7 @@
         <v>1720</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>1686.24</v>
       </c>
       <c r="E17" t="n">
         <v>1735</v>
@@ -1209,7 +1209,7 @@
         <v>1760</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>1770</v>
       </c>
       <c r="E18" t="n">
         <v>1730</v>
@@ -1259,7 +1259,7 @@
         <v>725</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>730</v>
       </c>
       <c r="E19" t="n">
         <v>725</v>
@@ -1309,7 +1309,7 @@
         <v>515</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>515</v>
       </c>
       <c r="E20" t="n">
         <v>530</v>
@@ -1359,7 +1359,7 @@
         <v>200</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>200</v>
       </c>
       <c r="E21" t="n">
         <v>192</v>
@@ -1409,7 +1409,7 @@
         <v>630</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>690</v>
       </c>
       <c r="E22" t="n">
         <v>765</v>
@@ -1459,7 +1459,7 @@
         <v>63</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E23" t="n">
         <v>59</v>
@@ -1509,7 +1509,7 @@
         <v>137</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>137</v>
       </c>
       <c r="E24" t="n">
         <v>131</v>
@@ -1559,7 +1559,7 @@
         <v>254</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>256</v>
       </c>
       <c r="E25" t="n">
         <v>228</v>
@@ -1609,7 +1609,7 @@
         <v>244</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>220</v>
       </c>
       <c r="E26" t="n">
         <v>234</v>
@@ -1659,7 +1659,7 @@
         <v>190</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>190</v>
       </c>
       <c r="E27" t="n">
         <v>192</v>
@@ -1709,7 +1709,7 @@
         <v>8500</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>8600</v>
       </c>
       <c r="E28" t="n">
         <v>8650</v>
@@ -1759,7 +1759,7 @@
         <v>525</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>520</v>
       </c>
       <c r="E29" t="n">
         <v>510</v>
@@ -1809,7 +1809,7 @@
         <v>472</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>472</v>
       </c>
       <c r="E30" t="n">
         <v>484</v>
@@ -1859,7 +1859,7 @@
         <v>745</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>745</v>
       </c>
       <c r="E31" t="n">
         <v>770</v>
@@ -1909,7 +1909,7 @@
         <v>65</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E32" t="n">
         <v>62</v>
@@ -1959,7 +1959,7 @@
         <v>296</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>300</v>
       </c>
       <c r="E33" t="n">
         <v>290</v>
@@ -2009,7 +2009,7 @@
         <v>222</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>224</v>
       </c>
       <c r="E34" t="n">
         <v>220</v>
@@ -2059,7 +2059,7 @@
         <v>720</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>720</v>
       </c>
       <c r="E35" t="n">
         <v>735</v>
@@ -2109,7 +2109,7 @@
         <v>193</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>193</v>
       </c>
       <c r="E36" t="n">
         <v>199</v>
@@ -2159,7 +2159,7 @@
         <v>212</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>210</v>
       </c>
       <c r="E37" t="n">
         <v>206</v>
@@ -2209,7 +2209,7 @@
         <v>2520</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>2520</v>
       </c>
       <c r="E38" t="n">
         <v>2460</v>
@@ -2363,7 +2363,7 @@
         <v>1375</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>1420</v>
       </c>
       <c r="E5" t="n">
         <v>1715</v>
@@ -2413,7 +2413,7 @@
         <v>1455</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>1405.34</v>
       </c>
       <c r="E6" t="n">
         <v>1445</v>
@@ -2463,7 +2463,7 @@
         <v>1375</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>1420</v>
       </c>
       <c r="E7" t="n">
         <v>1715</v>
@@ -2513,7 +2513,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>240</v>
       </c>
       <c r="E8" t="n">
         <v>224</v>
@@ -2563,7 +2563,7 @@
         <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>590</v>
       </c>
       <c r="E9" t="n">
         <v>590</v>
@@ -2613,7 +2613,7 @@
         <v>258</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>256</v>
       </c>
       <c r="E10" t="n">
         <v>262</v>
@@ -2663,7 +2663,7 @@
         <v>366</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>360</v>
       </c>
       <c r="E11" t="n">
         <v>360</v>
@@ -2713,7 +2713,7 @@
         <v>442</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>444</v>
       </c>
       <c r="E12" t="n">
         <v>444</v>
@@ -2763,7 +2763,7 @@
         <v>159</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>159</v>
       </c>
       <c r="E13" t="n">
         <v>152</v>
@@ -2813,7 +2813,7 @@
         <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>103</v>
       </c>
       <c r="E14" t="n">
         <v>97</v>
@@ -2863,7 +2863,7 @@
         <v>1205</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1210</v>
       </c>
       <c r="E15" t="n">
         <v>1200</v>
@@ -2913,7 +2913,7 @@
         <v>166</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>174</v>
       </c>
       <c r="E16" t="n">
         <v>178</v>
@@ -2963,7 +2963,7 @@
         <v>2630</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>2660</v>
       </c>
       <c r="E17" t="n">
         <v>2610</v>
@@ -3013,7 +3013,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
         <v>50</v>
@@ -3063,7 +3063,7 @@
         <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
         <v>76</v>
@@ -3113,7 +3113,7 @@
         <v>131</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>130</v>
       </c>
       <c r="E20" t="n">
         <v>131</v>
@@ -3163,7 +3163,7 @@
         <v>124</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>126</v>
       </c>
       <c r="E21" t="n">
         <v>121</v>
@@ -3213,7 +3213,7 @@
         <v>4710</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>4710</v>
       </c>
       <c r="E22" t="n">
         <v>4680</v>
@@ -3263,7 +3263,7 @@
         <v>424</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>424</v>
       </c>
       <c r="E23" t="n">
         <v>424</v>
@@ -3313,7 +3313,7 @@
         <v>775</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>720</v>
       </c>
       <c r="E24" t="n">
         <v>720</v>
@@ -3363,7 +3363,7 @@
         <v>114</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>115</v>
       </c>
       <c r="E25" t="n">
         <v>107</v>
@@ -3413,7 +3413,7 @@
         <v>64</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E26" t="n">
         <v>63</v>
@@ -3463,7 +3463,7 @@
         <v>248</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>248</v>
       </c>
       <c r="E27" t="n">
         <v>232</v>
@@ -3513,7 +3513,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>280</v>
       </c>
       <c r="E28" t="n">
         <v>324</v>
@@ -3563,7 +3563,7 @@
         <v>515</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>515</v>
       </c>
       <c r="E29" t="n">
         <v>530</v>
@@ -3613,7 +3613,7 @@
         <v>200</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>200</v>
       </c>
       <c r="E30" t="n">
         <v>192</v>
@@ -3663,7 +3663,7 @@
         <v>1195</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>1190</v>
       </c>
       <c r="E31" t="n">
         <v>1095</v>
@@ -3713,7 +3713,7 @@
         <v>166</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>164</v>
       </c>
       <c r="E32" t="n">
         <v>160</v>
@@ -3763,7 +3763,7 @@
         <v>975</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>970</v>
       </c>
       <c r="E33" t="n">
         <v>880</v>
@@ -3813,7 +3813,7 @@
         <v>133</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>133</v>
       </c>
       <c r="E34" t="n">
         <v>125</v>
@@ -3863,7 +3863,7 @@
         <v>114</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>114</v>
       </c>
       <c r="E35" t="n">
         <v>113</v>
@@ -3913,7 +3913,7 @@
         <v>63</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E36" t="n">
         <v>59</v>
@@ -3963,7 +3963,7 @@
         <v>122</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>123</v>
       </c>
       <c r="E37" t="n">
         <v>128</v>
@@ -4013,7 +4013,7 @@
         <v>210</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>212</v>
       </c>
       <c r="E38" t="n">
         <v>194</v>
@@ -4063,7 +4063,7 @@
         <v>216</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>258</v>
       </c>
       <c r="E39" t="n">
         <v>189</v>
@@ -4113,7 +4113,7 @@
         <v>254</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>256</v>
       </c>
       <c r="E40" t="n">
         <v>228</v>
@@ -4163,7 +4163,7 @@
         <v>244</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>220</v>
       </c>
       <c r="E41" t="n">
         <v>234</v>
@@ -4213,7 +4213,7 @@
         <v>73</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E42" t="n">
         <v>80</v>
@@ -4263,7 +4263,7 @@
         <v>154</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>155</v>
       </c>
       <c r="E43" t="n">
         <v>156</v>
@@ -4313,7 +4313,7 @@
         <v>121</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>122</v>
       </c>
       <c r="E44" t="n">
         <v>117</v>
@@ -4363,7 +4363,7 @@
         <v>226</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>226</v>
       </c>
       <c r="E45" t="n">
         <v>224</v>
@@ -4413,7 +4413,7 @@
         <v>1085</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>1085</v>
       </c>
       <c r="E46" t="n">
         <v>1090</v>
@@ -4463,7 +4463,7 @@
         <v>100</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>102</v>
       </c>
       <c r="E47" t="n">
         <v>101</v>
@@ -4513,7 +4513,7 @@
         <v>472</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>472</v>
       </c>
       <c r="E48" t="n">
         <v>484</v>
@@ -4563,7 +4563,7 @@
         <v>70</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E49" t="n">
         <v>67</v>
@@ -4613,7 +4613,7 @@
         <v>68</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E50" t="n">
         <v>67</v>
@@ -4663,7 +4663,7 @@
         <v>278</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>278</v>
       </c>
       <c r="E51" t="n">
         <v>270</v>
@@ -4713,7 +4713,7 @@
         <v>65</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E52" t="n">
         <v>62</v>
@@ -4763,7 +4763,7 @@
         <v>111</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E53" t="n">
         <v>111</v>
@@ -4813,7 +4813,7 @@
         <v>835</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>835</v>
       </c>
       <c r="E54" t="n">
         <v>905</v>
@@ -4863,7 +4863,7 @@
         <v>74</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>74</v>
       </c>
       <c r="E55" t="n">
         <v>75</v>
@@ -4913,7 +4913,7 @@
         <v>800</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>785</v>
       </c>
       <c r="E56" t="n">
         <v>770</v>
@@ -4963,7 +4963,7 @@
         <v>296</v>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>300</v>
       </c>
       <c r="E57" t="n">
         <v>290</v>
@@ -5013,7 +5013,7 @@
         <v>64</v>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>62</v>
       </c>
       <c r="E58" t="n">
         <v>63</v>
@@ -5063,7 +5063,7 @@
         <v>72</v>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>72</v>
       </c>
       <c r="E59" t="n">
         <v>71</v>
@@ -5113,7 +5113,7 @@
         <v>61</v>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>63</v>
       </c>
       <c r="E60" t="n">
         <v>60</v>
@@ -5163,7 +5163,7 @@
         <v>98</v>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>98</v>
       </c>
       <c r="E61" t="n">
         <v>95</v>
@@ -5213,7 +5213,7 @@
         <v>93</v>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>93</v>
       </c>
       <c r="E62" t="n">
         <v>88</v>
@@ -5263,7 +5263,7 @@
         <v>133</v>
       </c>
       <c r="D63" t="n">
-        <v/>
+        <v>135</v>
       </c>
       <c r="E63" t="n">
         <v>127</v>
@@ -5313,7 +5313,7 @@
         <v>212</v>
       </c>
       <c r="D64" t="n">
-        <v/>
+        <v>210</v>
       </c>
       <c r="E64" t="n">
         <v>206</v>
@@ -5363,7 +5363,7 @@
         <v>159</v>
       </c>
       <c r="D65" t="n">
-        <v/>
+        <v>159</v>
       </c>
       <c r="E65" t="n">
         <v>159</v>
@@ -5413,7 +5413,7 @@
         <v>238</v>
       </c>
       <c r="D66" t="n">
-        <v/>
+        <v>240</v>
       </c>
       <c r="E66" t="n">
         <v>236</v>
